--- a/output/pdf_financials_xlsx/FCD.UN.xlsx
+++ b/output/pdf_financials_xlsx/FCD.UN.xlsx
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000441</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002881</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.287989</v>
+        <v>0.287548</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.822015</v>
+        <v>3.819134</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>4.725642</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.287989</v>
+        <v>0.287548</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.822015</v>
+        <v>3.819134</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>4.725642</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>99.61604848166199</v>
+        <v>99.46350558113311</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -2135,13 +2135,13 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.43256</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.445297</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.947376</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.615352</v>
@@ -2227,13 +2227,13 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.239354</v>
+        <v>0.671914</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.212772</v>
+        <v>2.658069</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.178655</v>
+        <v>4.126031</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.615352</v>
@@ -2779,13 +2779,13 @@
         <v>0.081222</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.583084</v>
+        <v>0.150524</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.781359</v>
+        <v>0.336062</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.309225</v>
+        <v>2.361849</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.386452</v>
@@ -6320,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-3.066184</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-2.525569</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -6366,10 +6366,10 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-3.066184</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-2.525569</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -24585,7 +24585,11 @@
           <t>Repayment of Bank Indebtedness 6</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -28294,7 +28298,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -31398,7 +31402,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -39180,7 +39184,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -43417,7 +43421,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E468" s="5" t="n">
@@ -45519,7 +45523,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E494" s="5" t="n">
